--- a/artfynd/A 43477-2024 artfynd.xlsx
+++ b/artfynd/A 43477-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120316380</v>
       </c>
       <c r="B2" t="n">
-        <v>94321</v>
+        <v>94344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 43477-2024 artfynd.xlsx
+++ b/artfynd/A 43477-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120316380</v>
+        <v>120316388</v>
       </c>
       <c r="B2" t="n">
-        <v>94344</v>
+        <v>96885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ljusnevattnet, Vg</t>
+          <t>Långared, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345207</v>
+        <v>345211</v>
       </c>
       <c r="R2" t="n">
-        <v>6430545</v>
+        <v>6430576</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120316388</v>
+        <v>120316411</v>
       </c>
       <c r="B3" t="n">
-        <v>96862</v>
+        <v>97105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120316411</v>
+        <v>120316380</v>
       </c>
       <c r="B4" t="n">
-        <v>97082</v>
+        <v>94344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220686</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,14 +949,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långared, Vg</t>
+          <t>Ljusnevattnet, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345211</v>
+        <v>345207</v>
       </c>
       <c r="R4" t="n">
-        <v>6430576</v>
+        <v>6430545</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43477-2024 artfynd.xlsx
+++ b/artfynd/A 43477-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120316388</v>
+        <v>120316411</v>
       </c>
       <c r="B2" t="n">
-        <v>96885</v>
+        <v>97105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120316411</v>
+        <v>120316388</v>
       </c>
       <c r="B3" t="n">
-        <v>97105</v>
+        <v>96885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 43477-2024 artfynd.xlsx
+++ b/artfynd/A 43477-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120316411</v>
+        <v>120316388</v>
       </c>
       <c r="B2" t="n">
-        <v>97105</v>
+        <v>96885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120316388</v>
+        <v>120316411</v>
       </c>
       <c r="B3" t="n">
-        <v>96885</v>
+        <v>97105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -897,12 +897,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1014,12 +1014,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 43477-2024 artfynd.xlsx
+++ b/artfynd/A 43477-2024 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120975861</v>
+        <v>120975757</v>
       </c>
       <c r="B5" t="n">
-        <v>97029</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,46 +1038,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>345161</v>
+        <v>345343</v>
       </c>
       <c r="R5" t="n">
-        <v>6430612</v>
+        <v>6430292</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ett bestånd med mattlummer som hade sporax växte halvvägs upp på en bergknalle som var vitfärgad av renlavar.</t>
+          <t>Spillkråkehack vid basen av stammen hos ett torrträd av en tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1142,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120975757</v>
+        <v>120977648</v>
       </c>
       <c r="B6" t="n">
-        <v>57364</v>
+        <v>96708</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,46 +1153,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>345343</v>
+        <v>345190</v>
       </c>
       <c r="R6" t="n">
-        <v>6430292</v>
+        <v>6430370</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,17 +1223,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av stammen hos ett torrträd av en tall.</t>
+          <t>Växte på en 20 cm tjock ek vid en hällmarkskant väster om ett kärr. Nära 4 medelgrova aspar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,6 +1242,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1257,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120975727</v>
+        <v>120975861</v>
       </c>
       <c r="B7" t="n">
-        <v>57364</v>
+        <v>97039</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,46 +1273,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>224364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>345296</v>
+        <v>345161</v>
       </c>
       <c r="R7" t="n">
-        <v>6430217</v>
+        <v>6430612</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,7 +1349,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ett bohål som tillverkats av spillkråka i en grov och gammal tall. När det användes senast går inte att säga.</t>
+          <t>Ett bestånd med mattlummer som hade sporax växte halvvägs upp på en bergknalle som var vitfärgad av renlavar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,6 +1358,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1372,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120977077</v>
+        <v>120975598</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
+        <v>91973</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,43 +1393,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>345265</v>
+        <v>345182</v>
       </c>
       <c r="R8" t="n">
-        <v>6430176</v>
+        <v>6430332</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,17 +1458,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1,3-1,6 cm breda gnagspår på stammen hos ett 20 cm tjockt torrträd av en gran. Här satt även spår efter den vågbandade barkbocken.</t>
+          <t>Två övergångna, svarta dropptaggsvampar, dock årets fruktkroppar. Växte invid ett dike som rinner från ett kärr, vid foten av en medelgrov gran. I genomskärning visade köttet en mörk zonering ( mycket mörk på brun botten, ej blåaktigt) samt hade en del ljusa prickar i köttet. Mild smak. Gav ifrån sig röd vätska när jag klämde på en av fruktkropparna.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120977058</v>
+        <v>120977077</v>
       </c>
       <c r="B9" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,21 +1512,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1578,7 +1585,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>4-5 mm breda gnagspår som gick tydligt in i splintveden. Sneda ingångshål. Satt på ett 20 cm tjockt torrträd av en gran.</t>
+          <t>1,3-1,6 cm breda gnagspår på stammen hos ett 20 cm tjockt torrträd av en gran. Här satt även spår efter den vågbandade barkbocken.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120975598</v>
+        <v>120977058</v>
       </c>
       <c r="B10" t="n">
-        <v>91963</v>
+        <v>5189</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,45 +1629,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>345182</v>
+        <v>345265</v>
       </c>
       <c r="R10" t="n">
-        <v>6430332</v>
+        <v>6430176</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1687,17 +1692,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Två övergångna, svarta dropptaggsvampar, dock årets fruktkroppar. Växte invid ett dike som rinner från ett kärr, vid foten av en medelgrov gran. I genomskärning visade köttet en mörk zonering ( mycket mörk på brun botten, ej blåaktigt) samt hade en del ljusa prickar i köttet. Mild smak. Gav ifrån sig röd vätska när jag klämde på en av fruktkropparna.</t>
+          <t>4-5 mm breda gnagspår som gick tydligt in i splintveden. Sneda ingångshål. Satt på ett 20 cm tjockt torrträd av en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120977648</v>
+        <v>120975202</v>
       </c>
       <c r="B11" t="n">
-        <v>96698</v>
+        <v>97029</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,26 +1746,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>221944</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1773,14 +1774,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>345190</v>
+        <v>345227</v>
       </c>
       <c r="R11" t="n">
-        <v>6430370</v>
+        <v>6430555</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1807,17 +1808,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växte på en 20 cm tjock ek vid en hällmarkskant väster om ett kärr. Nära 4 medelgrova aspar.</t>
+          <t>Växte på en liten häll i nordöstra kanten på en lång men låg lodytemiljö.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120976753</v>
+        <v>120975276</v>
       </c>
       <c r="B12" t="n">
-        <v>96338</v>
+        <v>97029</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,23 +1862,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>221944</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2</t>
@@ -1897,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>345082</v>
+        <v>345126</v>
       </c>
       <c r="R12" t="n">
-        <v>6430449</v>
+        <v>6430476</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1933,11 +1930,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På en murken låga i kanten på en sumpskogsmiljö.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,7 +1960,7 @@
         <v>120975467</v>
       </c>
       <c r="B13" t="n">
-        <v>96698</v>
+        <v>96708</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2085,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120977586</v>
+        <v>120975727</v>
       </c>
       <c r="B14" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2123,20 +2115,20 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>345237</v>
+        <v>345296</v>
       </c>
       <c r="R14" t="n">
-        <v>6430314</v>
+        <v>6430217</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2163,17 +2155,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av ett medelgrovt torrträd av en tall.</t>
+          <t>Ett bohål som tillverkats av spillkråka i en grov och gammal tall. När det användes senast går inte att säga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120975202</v>
+        <v>120977586</v>
       </c>
       <c r="B15" t="n">
-        <v>97019</v>
+        <v>57367</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,46 +2204,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221944</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>345227</v>
+        <v>345237</v>
       </c>
       <c r="R15" t="n">
-        <v>6430555</v>
+        <v>6430314</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2278,17 +2270,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växte på en liten häll i nordöstra kanten på en lång men låg lodytemiljö.</t>
+          <t>Spillkråkehack vid basen av ett medelgrovt torrträd av en tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,7 +2289,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2316,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120975276</v>
+        <v>120977100</v>
       </c>
       <c r="B16" t="n">
-        <v>97019</v>
+        <v>57367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,46 +2319,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221944</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>345126</v>
+        <v>345297</v>
       </c>
       <c r="R16" t="n">
-        <v>6430476</v>
+        <v>6430196</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2394,12 +2385,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spår efter spillkråkans födosök vid basen hos ett torrträd av en tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,7 +2404,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2422,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120977100</v>
+        <v>120976753</v>
       </c>
       <c r="B17" t="n">
-        <v>57364</v>
+        <v>96348</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2439,46 +2434,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>345297</v>
+        <v>345082</v>
       </c>
       <c r="R17" t="n">
-        <v>6430196</v>
+        <v>6430449</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2505,17 +2504,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spår efter spillkråkans födosök vid basen hos ett torrträd av en tall.</t>
+          <t>På en murken låga i kanten på en sumpskogsmiljö.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,6 +2523,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>121091462</v>
       </c>
       <c r="B18" t="n">
-        <v>95657</v>
+        <v>95667</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>121121137</v>
       </c>
       <c r="B19" t="n">
-        <v>91305</v>
+        <v>91315</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 43477-2024 artfynd.xlsx
+++ b/artfynd/A 43477-2024 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120975757</v>
+        <v>120977648</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>96708</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,46 +1038,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>345343</v>
+        <v>345190</v>
       </c>
       <c r="R5" t="n">
-        <v>6430292</v>
+        <v>6430370</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,17 +1108,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av stammen hos ett torrträd av en tall.</t>
+          <t>Växte på en 20 cm tjock ek vid en hällmarkskant väster om ett kärr. Nära 4 medelgrova aspar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,6 +1127,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120977648</v>
+        <v>120975757</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>57367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,50 +1158,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>345190</v>
+        <v>345343</v>
       </c>
       <c r="R6" t="n">
-        <v>6430370</v>
+        <v>6430292</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,17 +1224,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växte på en 20 cm tjock ek vid en hällmarkskant väster om ett kärr. Nära 4 medelgrova aspar.</t>
+          <t>Spillkråkehack vid basen av stammen hos ett torrträd av en tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,7 +1243,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43477-2024 artfynd.xlsx
+++ b/artfynd/A 43477-2024 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120977648</v>
+        <v>120975757</v>
       </c>
       <c r="B5" t="n">
-        <v>96708</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,50 +1038,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>345190</v>
+        <v>345343</v>
       </c>
       <c r="R5" t="n">
-        <v>6430370</v>
+        <v>6430292</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,17 +1104,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växte på en 20 cm tjock ek vid en hällmarkskant väster om ett kärr. Nära 4 medelgrova aspar.</t>
+          <t>Spillkråkehack vid basen av stammen hos ett torrträd av en tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1123,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1146,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120975757</v>
+        <v>120977648</v>
       </c>
       <c r="B6" t="n">
-        <v>57367</v>
+        <v>96708</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,46 +1153,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>345343</v>
+        <v>345190</v>
       </c>
       <c r="R6" t="n">
-        <v>6430292</v>
+        <v>6430370</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,17 +1223,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av stammen hos ett torrträd av en tall.</t>
+          <t>Växte på en 20 cm tjock ek vid en hällmarkskant väster om ett kärr. Nära 4 medelgrova aspar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,6 +1242,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120975276</v>
+        <v>120975727</v>
       </c>
       <c r="B12" t="n">
-        <v>97029</v>
+        <v>57367</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,46 +1858,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221944</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>345126</v>
+        <v>345296</v>
       </c>
       <c r="R12" t="n">
-        <v>6430476</v>
+        <v>6430217</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1932,13 +1932,17 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett bohål som tillverkats av spillkråka i en grov och gammal tall. När det användes senast går inte att säga.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2077,10 +2081,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120975727</v>
+        <v>120975276</v>
       </c>
       <c r="B14" t="n">
-        <v>57367</v>
+        <v>97029</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,46 +2093,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221944</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>345296</v>
+        <v>345126</v>
       </c>
       <c r="R14" t="n">
-        <v>6430217</v>
+        <v>6430476</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2163,17 +2167,13 @@
           <t>2024-10-30</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ett bohål som tillverkats av spillkråka i en grov och gammal tall. När det användes senast går inte att säga.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43477-2024 artfynd.xlsx
+++ b/artfynd/A 43477-2024 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120975757</v>
+        <v>120975598</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>91973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,46 +1038,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>345343</v>
+        <v>345182</v>
       </c>
       <c r="R5" t="n">
-        <v>6430292</v>
+        <v>6430332</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1117,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av stammen hos ett torrträd av en tall.</t>
+          <t>Två övergångna, svarta dropptaggsvampar, dock årets fruktkroppar. Växte invid ett dike som rinner från ett kärr, vid foten av en medelgrov gran. I genomskärning visade köttet en mörk zonering ( mycket mörk på brun botten, ej blåaktigt) samt hade en del ljusa prickar i köttet. Mild smak. Gav ifrån sig röd vätska när jag klämde på en av fruktkropparna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,6 +1126,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120977648</v>
+        <v>120977077</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>5169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,46 +1161,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>345190</v>
+        <v>345265</v>
       </c>
       <c r="R6" t="n">
-        <v>6430370</v>
+        <v>6430176</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,7 +1234,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växte på en 20 cm tjock ek vid en hällmarkskant väster om ett kärr. Nära 4 medelgrova aspar.</t>
+          <t>1,3-1,6 cm breda gnagspår på stammen hos ett 20 cm tjockt torrträd av en gran. Här satt även spår efter den vågbandade barkbocken.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120975861</v>
+        <v>120977058</v>
       </c>
       <c r="B7" t="n">
-        <v>97039</v>
+        <v>5189</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,42 +1278,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224364</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>345161</v>
+        <v>345265</v>
       </c>
       <c r="R7" t="n">
-        <v>6430612</v>
+        <v>6430176</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1339,17 +1341,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ett bestånd med mattlummer som hade sporax växte halvvägs upp på en bergknalle som var vitfärgad av renlavar.</t>
+          <t>4-5 mm breda gnagspår som gick tydligt in i splintveden. Sneda ingångshål. Satt på ett 20 cm tjockt torrträd av en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120975598</v>
+        <v>120976753</v>
       </c>
       <c r="B8" t="n">
-        <v>91973</v>
+        <v>96348</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1395,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1417,21 +1419,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>345182</v>
+        <v>345082</v>
       </c>
       <c r="R8" t="n">
-        <v>6430332</v>
+        <v>6430449</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1468,7 +1471,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Två övergångna, svarta dropptaggsvampar, dock årets fruktkroppar. Växte invid ett dike som rinner från ett kärr, vid foten av en medelgrov gran. I genomskärning visade köttet en mörk zonering ( mycket mörk på brun botten, ej blåaktigt) samt hade en del ljusa prickar i köttet. Mild smak. Gav ifrån sig röd vätska när jag klämde på en av fruktkropparna.</t>
+          <t>På en murken låga i kanten på en sumpskogsmiljö.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120977077</v>
+        <v>120977648</v>
       </c>
       <c r="B9" t="n">
-        <v>5169</v>
+        <v>96708</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,43 +1515,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>2606</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>345265</v>
+        <v>345190</v>
       </c>
       <c r="R9" t="n">
-        <v>6430176</v>
+        <v>6430370</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1585,7 +1591,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1,3-1,6 cm breda gnagspår på stammen hos ett 20 cm tjockt torrträd av en gran. Här satt även spår efter den vågbandade barkbocken.</t>
+          <t>Växte på en 20 cm tjock ek vid en hällmarkskant väster om ett kärr. Nära 4 medelgrova aspar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120977058</v>
+        <v>120975757</v>
       </c>
       <c r="B10" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,20 +1631,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1647,12 +1653,11 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>345265</v>
+        <v>345343</v>
       </c>
       <c r="R10" t="n">
-        <v>6430176</v>
+        <v>6430292</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1692,17 +1697,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>4-5 mm breda gnagspår som gick tydligt in i splintveden. Sneda ingångshål. Satt på ett 20 cm tjockt torrträd av en gran.</t>
+          <t>Spillkråkehack vid basen av stammen hos ett torrträd av en tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1716,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1730,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120975202</v>
+        <v>120977100</v>
       </c>
       <c r="B11" t="n">
-        <v>97029</v>
+        <v>57367</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,46 +1746,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221944</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>345227</v>
+        <v>345297</v>
       </c>
       <c r="R11" t="n">
-        <v>6430555</v>
+        <v>6430196</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1808,17 +1812,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växte på en liten häll i nordöstra kanten på en lång men låg lodytemiljö.</t>
+          <t>Spår efter spillkråkans födosök vid basen hos ett torrträd av en tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,7 +1831,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1846,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120975727</v>
+        <v>120975202</v>
       </c>
       <c r="B12" t="n">
-        <v>57367</v>
+        <v>97029</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,46 +1861,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221944</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>345296</v>
+        <v>345227</v>
       </c>
       <c r="R12" t="n">
-        <v>6430217</v>
+        <v>6430555</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1934,7 +1937,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ett bohål som tillverkats av spillkråka i en grov och gammal tall. När det användes senast går inte att säga.</t>
+          <t>Växte på en liten häll i nordöstra kanten på en lång men låg lodytemiljö.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,6 +1946,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2081,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120975276</v>
+        <v>120975861</v>
       </c>
       <c r="B14" t="n">
-        <v>97029</v>
+        <v>97039</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,27 +2101,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221944</v>
+        <v>224364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
+          <t>Lycopodium clavatum subsp. clavatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2129,10 +2133,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>345126</v>
+        <v>345161</v>
       </c>
       <c r="R14" t="n">
-        <v>6430476</v>
+        <v>6430612</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2165,6 +2169,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ett bestånd med mattlummer som hade sporax växte halvvägs upp på en bergknalle som var vitfärgad av renlavar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,7 +2201,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120977586</v>
+        <v>120975727</v>
       </c>
       <c r="B15" t="n">
         <v>57367</v>
@@ -2230,20 +2239,20 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>345237</v>
+        <v>345296</v>
       </c>
       <c r="R15" t="n">
-        <v>6430314</v>
+        <v>6430217</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2270,17 +2279,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av ett medelgrovt torrträd av en tall.</t>
+          <t>Ett bohål som tillverkats av spillkråka i en grov och gammal tall. När det användes senast går inte att säga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2316,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120977100</v>
+        <v>120975276</v>
       </c>
       <c r="B16" t="n">
-        <v>57367</v>
+        <v>97029</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2319,46 +2328,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>221944</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>345297</v>
+        <v>345126</v>
       </c>
       <c r="R16" t="n">
-        <v>6430196</v>
+        <v>6430476</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2385,17 +2394,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spår efter spillkråkans födosök vid basen hos ett torrträd av en tall.</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,6 +2408,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2422,10 +2427,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120976753</v>
+        <v>120977586</v>
       </c>
       <c r="B17" t="n">
-        <v>96348</v>
+        <v>57367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2434,50 +2439,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>345082</v>
+        <v>345237</v>
       </c>
       <c r="R17" t="n">
-        <v>6430449</v>
+        <v>6430314</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2504,17 +2505,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På en murken låga i kanten på en sumpskogsmiljö.</t>
+          <t>Spillkråkehack vid basen av ett medelgrovt torrträd av en tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,7 +2524,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43477-2024 artfynd.xlsx
+++ b/artfynd/A 43477-2024 artfynd.xlsx
@@ -1734,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120977100</v>
+        <v>120975202</v>
       </c>
       <c r="B11" t="n">
-        <v>57367</v>
+        <v>97029</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,46 +1746,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>221944</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>345297</v>
+        <v>345227</v>
       </c>
       <c r="R11" t="n">
-        <v>6430196</v>
+        <v>6430555</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1812,17 +1812,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spår efter spillkråkans födosök vid basen hos ett torrträd av en tall.</t>
+          <t>Växte på en liten häll i nordöstra kanten på en lång men låg lodytemiljö.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,6 +1831,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1849,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120975202</v>
+        <v>120977100</v>
       </c>
       <c r="B12" t="n">
-        <v>97029</v>
+        <v>57367</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,46 +1862,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221944</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>345227</v>
+        <v>345297</v>
       </c>
       <c r="R12" t="n">
-        <v>6430555</v>
+        <v>6430196</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1927,17 +1928,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Växte på en liten häll i nordöstra kanten på en lång men låg lodytemiljö.</t>
+          <t>Spår efter spillkråkans födosök vid basen hos ett torrträd av en tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,7 +1947,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120975467</v>
+        <v>120975861</v>
       </c>
       <c r="B13" t="n">
-        <v>96708</v>
+        <v>97039</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,23 +1981,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2606</v>
+        <v>224364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>1</t>
@@ -2005,7 +2001,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2013,14 +2009,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>345187</v>
+        <v>345161</v>
       </c>
       <c r="R13" t="n">
-        <v>6430352</v>
+        <v>6430612</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2057,7 +2053,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>En liten tuss på en av de medelgrova asparna som står på fastmarken i södra kanten på ett kärr.</t>
+          <t>Ett bestånd med mattlummer som hade sporax växte halvvägs upp på en bergknalle som var vitfärgad av renlavar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2085,10 +2081,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120975861</v>
+        <v>120975467</v>
       </c>
       <c r="B14" t="n">
-        <v>97039</v>
+        <v>96708</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2101,19 +2097,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224364</v>
+        <v>2606</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2129,14 +2129,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>345161</v>
+        <v>345187</v>
       </c>
       <c r="R14" t="n">
-        <v>6430612</v>
+        <v>6430352</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ett bestånd med mattlummer som hade sporax växte halvvägs upp på en bergknalle som var vitfärgad av renlavar.</t>
+          <t>En liten tuss på en av de medelgrova asparna som står på fastmarken i södra kanten på ett kärr.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 43477-2024 artfynd.xlsx
+++ b/artfynd/A 43477-2024 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120975598</v>
+        <v>120976753</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>96361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1066,21 +1066,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>345182</v>
+        <v>345082</v>
       </c>
       <c r="R5" t="n">
-        <v>6430332</v>
+        <v>6430449</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två övergångna, svarta dropptaggsvampar, dock årets fruktkroppar. Växte invid ett dike som rinner från ett kärr, vid foten av en medelgrov gran. I genomskärning visade köttet en mörk zonering ( mycket mörk på brun botten, ej blåaktigt) samt hade en del ljusa prickar i köttet. Mild smak. Gav ifrån sig röd vätska när jag klämde på en av fruktkropparna.</t>
+          <t>På en murken låga i kanten på en sumpskogsmiljö.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120977077</v>
+        <v>120975467</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>96721</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,43 +1162,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>345265</v>
+        <v>345187</v>
       </c>
       <c r="R6" t="n">
-        <v>6430176</v>
+        <v>6430352</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,17 +1228,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1,3-1,6 cm breda gnagspår på stammen hos ett 20 cm tjockt torrträd av en gran. Här satt även spår efter den vågbandade barkbocken.</t>
+          <t>En liten tuss på en av de medelgrova asparna som står på fastmarken i södra kanten på ett kärr.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1379,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120976753</v>
+        <v>120977077</v>
       </c>
       <c r="B8" t="n">
-        <v>96348</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,46 +1399,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>345082</v>
+        <v>345265</v>
       </c>
       <c r="R8" t="n">
-        <v>6430449</v>
+        <v>6430176</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1461,17 +1462,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en murken låga i kanten på en sumpskogsmiljö.</t>
+          <t>1,3-1,6 cm breda gnagspår på stammen hos ett 20 cm tjockt torrträd av en gran. Här satt även spår efter den vågbandade barkbocken.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1500,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120977648</v>
+        <v>120975861</v>
       </c>
       <c r="B9" t="n">
-        <v>96708</v>
+        <v>97052</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,23 +1516,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2606</v>
+        <v>224364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
@@ -1539,7 +1536,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1547,14 +1544,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>345190</v>
+        <v>345161</v>
       </c>
       <c r="R9" t="n">
-        <v>6430370</v>
+        <v>6430612</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1581,17 +1578,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växte på en 20 cm tjock ek vid en hällmarkskant väster om ett kärr. Nära 4 medelgrova aspar.</t>
+          <t>Ett bestånd med mattlummer som hade sporax växte halvvägs upp på en bergknalle som var vitfärgad av renlavar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,7 +1616,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120975757</v>
+        <v>120977100</v>
       </c>
       <c r="B10" t="n">
         <v>57367</v>
@@ -1667,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>345343</v>
+        <v>345297</v>
       </c>
       <c r="R10" t="n">
-        <v>6430292</v>
+        <v>6430196</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1697,17 +1694,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av stammen hos ett torrträd av en tall.</t>
+          <t>Spår efter spillkråkans födosök vid basen hos ett torrträd av en tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120975202</v>
+        <v>120975757</v>
       </c>
       <c r="B11" t="n">
-        <v>97029</v>
+        <v>57367</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,46 +1743,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221944</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>345227</v>
+        <v>345343</v>
       </c>
       <c r="R11" t="n">
-        <v>6430555</v>
+        <v>6430292</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1822,7 +1819,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växte på en liten häll i nordöstra kanten på en lång men låg lodytemiljö.</t>
+          <t>Spillkråkehack vid basen av stammen hos ett torrträd av en tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,7 +1828,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1850,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120977100</v>
+        <v>120975598</v>
       </c>
       <c r="B12" t="n">
-        <v>57367</v>
+        <v>91985</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,46 +1858,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>345297</v>
+        <v>345182</v>
       </c>
       <c r="R12" t="n">
-        <v>6430196</v>
+        <v>6430332</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1928,17 +1927,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Spår efter spillkråkans födosök vid basen hos ett torrträd av en tall.</t>
+          <t>Två övergångna, svarta dropptaggsvampar, dock årets fruktkroppar. Växte invid ett dike som rinner från ett kärr, vid foten av en medelgrov gran. I genomskärning visade köttet en mörk zonering ( mycket mörk på brun botten, ej blåaktigt) samt hade en del ljusa prickar i köttet. Mild smak. Gav ifrån sig röd vätska när jag klämde på en av fruktkropparna.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,6 +1946,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120975861</v>
+        <v>120977648</v>
       </c>
       <c r="B13" t="n">
-        <v>97039</v>
+        <v>96721</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,19 +1981,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224364</v>
+        <v>2606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>1</t>
@@ -2001,7 +2005,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2009,14 +2013,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>345161</v>
+        <v>345190</v>
       </c>
       <c r="R13" t="n">
-        <v>6430612</v>
+        <v>6430370</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2043,17 +2047,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ett bestånd med mattlummer som hade sporax växte halvvägs upp på en bergknalle som var vitfärgad av renlavar.</t>
+          <t>Växte på en 20 cm tjock ek vid en hällmarkskant väster om ett kärr. Nära 4 medelgrova aspar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120975467</v>
+        <v>120975276</v>
       </c>
       <c r="B14" t="n">
-        <v>96708</v>
+        <v>97042</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,26 +2101,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2606</v>
+        <v>221944</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2129,14 +2129,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>345187</v>
+        <v>345126</v>
       </c>
       <c r="R14" t="n">
-        <v>6430352</v>
+        <v>6430476</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2169,11 +2169,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>En liten tuss på en av de medelgrova asparna som står på fastmarken i södra kanten på ett kärr.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120975727</v>
+        <v>120975202</v>
       </c>
       <c r="B15" t="n">
-        <v>57367</v>
+        <v>97042</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2213,46 +2208,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>221944</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Valås, söder om, Vg</t>
+          <t>Valås, väster om, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>345296</v>
+        <v>345227</v>
       </c>
       <c r="R15" t="n">
-        <v>6430217</v>
+        <v>6430555</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2289,7 +2284,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ett bohål som tillverkats av spillkråka i en grov och gammal tall. När det användes senast går inte att säga.</t>
+          <t>Växte på en liten häll i nordöstra kanten på en lång men låg lodytemiljö.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,6 +2293,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2316,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120975276</v>
+        <v>120977586</v>
       </c>
       <c r="B16" t="n">
-        <v>97029</v>
+        <v>57367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,46 +2324,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221944</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valås, väster om, Vg</t>
+          <t>Valås, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>345126</v>
+        <v>345237</v>
       </c>
       <c r="R16" t="n">
-        <v>6430476</v>
+        <v>6430314</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2394,12 +2390,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spillkråkehack vid basen av ett medelgrovt torrträd av en tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,7 +2409,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120977586</v>
+        <v>120975727</v>
       </c>
       <c r="B17" t="n">
         <v>57367</v>
@@ -2465,20 +2465,20 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Valås, sydväst om, Vg</t>
+          <t>Valås, söder om, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>345237</v>
+        <v>345296</v>
       </c>
       <c r="R17" t="n">
-        <v>6430314</v>
+        <v>6430217</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2505,17 +2505,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av ett medelgrovt torrträd av en tall.</t>
+          <t>Ett bohål som tillverkats av spillkråka i en grov och gammal tall. När det användes senast går inte att säga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,7 +2545,7 @@
         <v>121091462</v>
       </c>
       <c r="B18" t="n">
-        <v>95667</v>
+        <v>95680</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>121121137</v>
       </c>
       <c r="B19" t="n">
-        <v>91315</v>
+        <v>91327</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 43477-2024 artfynd.xlsx
+++ b/artfynd/A 43477-2024 artfynd.xlsx
@@ -2545,7 +2545,7 @@
         <v>121091462</v>
       </c>
       <c r="B18" t="n">
-        <v>95680</v>
+        <v>95681</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>121121137</v>
       </c>
       <c r="B19" t="n">
-        <v>91327</v>
+        <v>91328</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 43477-2024 artfynd.xlsx
+++ b/artfynd/A 43477-2024 artfynd.xlsx
@@ -2545,7 +2545,7 @@
         <v>121091462</v>
       </c>
       <c r="B18" t="n">
-        <v>95681</v>
+        <v>95684</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>121121137</v>
       </c>
       <c r="B19" t="n">
-        <v>91328</v>
+        <v>91331</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
